--- a/artfynd/A 19645-2026 artfynd.xlsx
+++ b/artfynd/A 19645-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -897,6 +897,779 @@
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>134033032</v>
+      </c>
+      <c r="B4" t="n">
+        <v>57955</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Stuttjärnsfall stora omr S, Vstm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>498798</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6630831</v>
+      </c>
+      <c r="S4" t="n">
+        <v>100</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Ljusnarsberg</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Ljusnarsberg</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Maria Berdén Evertsson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Maria Berdén Evertsson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Örebro län LB</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>134032013</v>
+      </c>
+      <c r="B5" t="n">
+        <v>58217</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>102981</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Hussvala</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Delichon urbicum</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Stuttjärnsfall stora omr S, Vstm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>498798</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6630831</v>
+      </c>
+      <c r="S5" t="n">
+        <v>100</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Ljusnarsberg</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Ljusnarsberg</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Maria Berdén Evertsson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Maria Berdén Evertsson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Örebro län LB</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>134032994</v>
+      </c>
+      <c r="B6" t="n">
+        <v>58440</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>100058</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Mindre flugsnappare</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Ficedula parva</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Bechstein, 1794)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Stuttjärnsfall stora omr S, Vstm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>498798</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6630831</v>
+      </c>
+      <c r="S6" t="n">
+        <v>100</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Ljusnarsberg</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Ljusnarsberg</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Maria Berdén Evertsson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Maria Berdén Evertsson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Örebro län LB</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>134032932</v>
+      </c>
+      <c r="B7" t="n">
+        <v>57263</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>100065</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Trana</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Grus grus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Stuttjärnsfall stora omr S, Vstm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>498798</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6630831</v>
+      </c>
+      <c r="S7" t="n">
+        <v>100</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Ljusnarsberg</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Ljusnarsberg</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Maria Berdén Evertsson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Maria Berdén Evertsson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Örebro län LB</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>134033641</v>
+      </c>
+      <c r="B8" t="n">
+        <v>57369</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>102954</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Enkelbeckasin</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Gallinago gallinago</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Stuttjärnsfall stora omr S, Vstm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>498798</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6630831</v>
+      </c>
+      <c r="S8" t="n">
+        <v>100</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Ljusnarsberg</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Ljusnarsberg</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Spelflykt</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Maria Berdén Evertsson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Maria Berdén Evertsson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Örebro län LB</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>134033720</v>
+      </c>
+      <c r="B9" t="n">
+        <v>57779</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>102976</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Tornseglare</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Apus apus</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Stuttjärnsfall stora omr S, Vstm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>498798</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6630831</v>
+      </c>
+      <c r="S9" t="n">
+        <v>100</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Ljusnarsberg</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Ljusnarsberg</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Maria Berdén Evertsson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Maria Berdén Evertsson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Örebro län LB</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>134031752</v>
+      </c>
+      <c r="B10" t="n">
+        <v>57607</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>100063</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Smålom</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Gavia stellata</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Pontoppidan, 1763)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Stuttjärnsfall stora omr S, Vstm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>498798</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6630831</v>
+      </c>
+      <c r="S10" t="n">
+        <v>100</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Ljusnarsberg</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Ljusnarsberg</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Från närbelägen sjö eller våtmark</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Maria Berdén Evertsson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Maria Berdén Evertsson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Örebro län LB</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 19645-2026 artfynd.xlsx
+++ b/artfynd/A 19645-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AY14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -899,27 +899,27 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>134033032</v>
+        <v>134045236</v>
       </c>
       <c r="B4" t="n">
-        <v>57955</v>
+        <v>58332</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>103015</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -1008,32 +1008,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>134032013</v>
+        <v>134045231</v>
       </c>
       <c r="B5" t="n">
-        <v>58217</v>
+        <v>58444</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>102981</v>
+        <v>103018</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Hussvala</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Delichon urbicum</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pallas, 1764)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1117,32 +1117,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>134032994</v>
+        <v>134045219</v>
       </c>
       <c r="B6" t="n">
-        <v>58440</v>
+        <v>58243</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100058</v>
+        <v>103012</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mindre flugsnappare</t>
+          <t>Grönsångare</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Ficedula parva</t>
+          <t>Phylloscopus sibilatrix</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Bechstein, 1794)</t>
+          <t>(Bechstein, 1793)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1226,27 +1226,27 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>134032932</v>
+        <v>134033032</v>
       </c>
       <c r="B7" t="n">
-        <v>57263</v>
+        <v>57955</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100065</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Trana</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Grus grus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1335,27 +1335,27 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>134033641</v>
+        <v>134032013</v>
       </c>
       <c r="B8" t="n">
-        <v>57369</v>
+        <v>58217</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>102954</v>
+        <v>102981</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Enkelbeckasin</t>
+          <t>Hussvala</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Gallinago gallinago</t>
+          <t>Delichon urbicum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1416,11 +1416,6 @@
           <t>2026-05-27</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Spelflykt</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
@@ -1449,32 +1444,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>134033720</v>
+        <v>134032994</v>
       </c>
       <c r="B9" t="n">
-        <v>57779</v>
+        <v>58440</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>102976</v>
+        <v>100058</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tornseglare</t>
+          <t>Mindre flugsnappare</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Apus apus</t>
+          <t>Ficedula parva</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Bechstein, 1794)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1558,32 +1553,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>134031752</v>
+        <v>134032932</v>
       </c>
       <c r="B10" t="n">
-        <v>57607</v>
+        <v>57263</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100063</v>
+        <v>100065</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Smålom</t>
+          <t>Trana</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Gavia stellata</t>
+          <t>Grus grus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Pontoppidan, 1763)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1639,11 +1634,6 @@
           <t>2026-05-27</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Från närbelägen sjö eller våtmark</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
@@ -1665,6 +1655,452 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Örebro län LB</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>134033641</v>
+      </c>
+      <c r="B11" t="n">
+        <v>57369</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>102954</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Enkelbeckasin</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Gallinago gallinago</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Stuttjärnsfall stora omr S, Vstm</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>498798</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6630831</v>
+      </c>
+      <c r="S11" t="n">
+        <v>100</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Ljusnarsberg</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Ljusnarsberg</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Spelflykt</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Maria Berdén Evertsson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Maria Berdén Evertsson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Örebro län LB</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>134045177</v>
+      </c>
+      <c r="B12" t="n">
+        <v>58641</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>103044</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Grönsiska</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Spinus spinus</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Stuttjärnsfall stora omr S, Vstm</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>498798</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6630831</v>
+      </c>
+      <c r="S12" t="n">
+        <v>100</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Ljusnarsberg</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Ljusnarsberg</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Maria Berdén Evertsson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Maria Berdén Evertsson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Örebro län LB</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>134033720</v>
+      </c>
+      <c r="B13" t="n">
+        <v>57779</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>102976</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Tornseglare</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Apus apus</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Stuttjärnsfall stora omr S, Vstm</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>498798</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6630831</v>
+      </c>
+      <c r="S13" t="n">
+        <v>100</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Ljusnarsberg</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Ljusnarsberg</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Maria Berdén Evertsson</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Maria Berdén Evertsson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Örebro län LB</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>134031752</v>
+      </c>
+      <c r="B14" t="n">
+        <v>57607</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>100063</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Smålom</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Gavia stellata</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Pontoppidan, 1763)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Stuttjärnsfall stora omr S, Vstm</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>498798</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6630831</v>
+      </c>
+      <c r="S14" t="n">
+        <v>100</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Ljusnarsberg</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Ljusnarsberg</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Från närbelägen sjö eller våtmark</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Maria Berdén Evertsson</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Maria Berdén Evertsson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr">
         <is>
           <t>Naturskyddsföreningen Örebro län LB</t>
         </is>

--- a/artfynd/A 19645-2026 artfynd.xlsx
+++ b/artfynd/A 19645-2026 artfynd.xlsx
@@ -1444,10 +1444,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>134032994</v>
+        <v>134032932</v>
       </c>
       <c r="B9" t="n">
-        <v>58440</v>
+        <v>57263</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1455,21 +1455,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100058</v>
+        <v>100065</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mindre flugsnappare</t>
+          <t>Trana</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Ficedula parva</t>
+          <t>Grus grus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Bechstein, 1794)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1553,10 +1553,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>134032932</v>
+        <v>134032994</v>
       </c>
       <c r="B10" t="n">
-        <v>57263</v>
+        <v>58440</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1564,21 +1564,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100065</v>
+        <v>100058</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Trana</t>
+          <t>Mindre flugsnappare</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Grus grus</t>
+          <t>Ficedula parva</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Bechstein, 1794)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>

--- a/artfynd/A 19645-2026 artfynd.xlsx
+++ b/artfynd/A 19645-2026 artfynd.xlsx
@@ -902,7 +902,7 @@
         <v>134045236</v>
       </c>
       <c r="B4" t="n">
-        <v>58332</v>
+        <v>58339</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         <v>134045231</v>
       </c>
       <c r="B5" t="n">
-        <v>58444</v>
+        <v>58451</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1120,7 +1120,7 @@
         <v>134045219</v>
       </c>
       <c r="B6" t="n">
-        <v>58243</v>
+        <v>58250</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1226,27 +1226,27 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>134033032</v>
+        <v>134032013</v>
       </c>
       <c r="B7" t="n">
-        <v>57955</v>
+        <v>58224</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>102981</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Hussvala</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Delichon urbicum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1335,27 +1335,27 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>134032013</v>
+        <v>134033032</v>
       </c>
       <c r="B8" t="n">
-        <v>58217</v>
+        <v>57962</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>102981</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Hussvala</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Delichon urbicum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1444,10 +1444,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>134032932</v>
+        <v>134032994</v>
       </c>
       <c r="B9" t="n">
-        <v>57263</v>
+        <v>58447</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1455,21 +1455,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100065</v>
+        <v>100058</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Trana</t>
+          <t>Mindre flugsnappare</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Grus grus</t>
+          <t>Ficedula parva</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Bechstein, 1794)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1553,10 +1553,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>134032994</v>
+        <v>134032932</v>
       </c>
       <c r="B10" t="n">
-        <v>58440</v>
+        <v>57270</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1564,21 +1564,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100058</v>
+        <v>100065</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mindre flugsnappare</t>
+          <t>Trana</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Ficedula parva</t>
+          <t>Grus grus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Bechstein, 1794)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1665,7 +1665,7 @@
         <v>134033641</v>
       </c>
       <c r="B11" t="n">
-        <v>57369</v>
+        <v>57376</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1779,7 +1779,7 @@
         <v>134045177</v>
       </c>
       <c r="B12" t="n">
-        <v>58641</v>
+        <v>58648</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1888,7 +1888,7 @@
         <v>134033720</v>
       </c>
       <c r="B13" t="n">
-        <v>57779</v>
+        <v>57786</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1997,7 +1997,7 @@
         <v>134031752</v>
       </c>
       <c r="B14" t="n">
-        <v>57607</v>
+        <v>57614</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 19645-2026 artfynd.xlsx
+++ b/artfynd/A 19645-2026 artfynd.xlsx
@@ -1226,27 +1226,27 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>134032013</v>
+        <v>134033032</v>
       </c>
       <c r="B7" t="n">
-        <v>58224</v>
+        <v>57962</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>102981</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Hussvala</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Delichon urbicum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1335,27 +1335,27 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>134033032</v>
+        <v>134032013</v>
       </c>
       <c r="B8" t="n">
-        <v>57962</v>
+        <v>58224</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>102981</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Hussvala</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Delichon urbicum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1885,32 +1885,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>134033720</v>
+        <v>134031752</v>
       </c>
       <c r="B13" t="n">
-        <v>57786</v>
+        <v>57614</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>102976</v>
+        <v>100063</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tornseglare</t>
+          <t>Smålom</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Apus apus</t>
+          <t>Gavia stellata</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pontoppidan, 1763)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1966,6 +1966,11 @@
           <t>2026-05-27</t>
         </is>
       </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Från närbelägen sjö eller våtmark</t>
+        </is>
+      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
@@ -1994,32 +1999,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>134031752</v>
+        <v>134033720</v>
       </c>
       <c r="B14" t="n">
-        <v>57614</v>
+        <v>57786</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100063</v>
+        <v>102976</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Smålom</t>
+          <t>Tornseglare</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Gavia stellata</t>
+          <t>Apus apus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Pontoppidan, 1763)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2075,11 +2080,6 @@
           <t>2026-05-27</t>
         </is>
       </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Från närbelägen sjö eller våtmark</t>
-        </is>
-      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 19645-2026 artfynd.xlsx
+++ b/artfynd/A 19645-2026 artfynd.xlsx
@@ -902,7 +902,7 @@
         <v>134045236</v>
       </c>
       <c r="B4" t="n">
-        <v>58339</v>
+        <v>58349</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         <v>134045231</v>
       </c>
       <c r="B5" t="n">
-        <v>58451</v>
+        <v>58461</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1120,7 +1120,7 @@
         <v>134045219</v>
       </c>
       <c r="B6" t="n">
-        <v>58250</v>
+        <v>58260</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1226,27 +1226,27 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>134033032</v>
+        <v>134032013</v>
       </c>
       <c r="B7" t="n">
-        <v>57962</v>
+        <v>58234</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>102981</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Hussvala</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Delichon urbicum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1335,27 +1335,27 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>134032013</v>
+        <v>134033032</v>
       </c>
       <c r="B8" t="n">
-        <v>58224</v>
+        <v>57972</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>102981</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Hussvala</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Delichon urbicum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1447,7 +1447,7 @@
         <v>134032994</v>
       </c>
       <c r="B9" t="n">
-        <v>58447</v>
+        <v>58457</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1556,7 +1556,7 @@
         <v>134032932</v>
       </c>
       <c r="B10" t="n">
-        <v>57270</v>
+        <v>57280</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1665,7 +1665,7 @@
         <v>134033641</v>
       </c>
       <c r="B11" t="n">
-        <v>57376</v>
+        <v>57386</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1779,7 +1779,7 @@
         <v>134045177</v>
       </c>
       <c r="B12" t="n">
-        <v>58648</v>
+        <v>58658</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1888,7 +1888,7 @@
         <v>134031752</v>
       </c>
       <c r="B13" t="n">
-        <v>57614</v>
+        <v>57624</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2002,7 +2002,7 @@
         <v>134033720</v>
       </c>
       <c r="B14" t="n">
-        <v>57786</v>
+        <v>57796</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 19645-2026 artfynd.xlsx
+++ b/artfynd/A 19645-2026 artfynd.xlsx
@@ -1885,32 +1885,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>134031752</v>
+        <v>134033720</v>
       </c>
       <c r="B13" t="n">
-        <v>57624</v>
+        <v>57796</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100063</v>
+        <v>102976</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Smålom</t>
+          <t>Tornseglare</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Gavia stellata</t>
+          <t>Apus apus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Pontoppidan, 1763)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1966,11 +1966,6 @@
           <t>2026-05-27</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Från närbelägen sjö eller våtmark</t>
-        </is>
-      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
@@ -1999,32 +1994,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>134033720</v>
+        <v>134031752</v>
       </c>
       <c r="B14" t="n">
-        <v>57796</v>
+        <v>57624</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>102976</v>
+        <v>100063</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tornseglare</t>
+          <t>Smålom</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Apus apus</t>
+          <t>Gavia stellata</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pontoppidan, 1763)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2080,6 +2075,11 @@
           <t>2026-05-27</t>
         </is>
       </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Från närbelägen sjö eller våtmark</t>
+        </is>
+      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 19645-2026 artfynd.xlsx
+++ b/artfynd/A 19645-2026 artfynd.xlsx
@@ -1885,32 +1885,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>134033720</v>
+        <v>134031752</v>
       </c>
       <c r="B13" t="n">
-        <v>57796</v>
+        <v>57624</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>102976</v>
+        <v>100063</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tornseglare</t>
+          <t>Smålom</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Apus apus</t>
+          <t>Gavia stellata</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pontoppidan, 1763)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1966,6 +1966,11 @@
           <t>2026-05-27</t>
         </is>
       </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Från närbelägen sjö eller våtmark</t>
+        </is>
+      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
@@ -1994,32 +1999,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>134031752</v>
+        <v>134033720</v>
       </c>
       <c r="B14" t="n">
-        <v>57624</v>
+        <v>57796</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100063</v>
+        <v>102976</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Smålom</t>
+          <t>Tornseglare</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Gavia stellata</t>
+          <t>Apus apus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Pontoppidan, 1763)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2075,11 +2080,6 @@
           <t>2026-05-27</t>
         </is>
       </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Från närbelägen sjö eller våtmark</t>
-        </is>
-      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 19645-2026 artfynd.xlsx
+++ b/artfynd/A 19645-2026 artfynd.xlsx
@@ -1226,27 +1226,27 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>134032013</v>
+        <v>134033032</v>
       </c>
       <c r="B7" t="n">
-        <v>58234</v>
+        <v>57972</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>102981</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Hussvala</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Delichon urbicum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1335,27 +1335,27 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>134033032</v>
+        <v>134032013</v>
       </c>
       <c r="B8" t="n">
-        <v>57972</v>
+        <v>58234</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>102981</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Hussvala</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Delichon urbicum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">

--- a/artfynd/A 19645-2026 artfynd.xlsx
+++ b/artfynd/A 19645-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY14"/>
+  <dimension ref="A1:AY15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,7 @@
         <v>121853586</v>
       </c>
       <c r="B2" t="n">
-        <v>94793</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96554</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,12 +785,7 @@
         <v>121853587</v>
       </c>
       <c r="B3" t="n">
-        <v>91462</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92632</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -899,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>134045236</v>
+        <v>134033032</v>
       </c>
       <c r="B4" t="n">
-        <v>58349</v>
+        <v>57972</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -910,16 +900,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103015</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -1008,32 +998,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>134045231</v>
+        <v>134032994</v>
       </c>
       <c r="B5" t="n">
-        <v>58461</v>
+        <v>58457</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103018</v>
+        <v>100058</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Mindre flugsnappare</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Ficedula parva</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
+          <t>(Bechstein, 1794)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1117,32 +1107,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>134045219</v>
+        <v>134031752</v>
       </c>
       <c r="B6" t="n">
-        <v>58260</v>
+        <v>57624</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103012</v>
+        <v>100063</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Grönsångare</t>
+          <t>Smålom</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phylloscopus sibilatrix</t>
+          <t>Gavia stellata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Bechstein, 1793)</t>
+          <t>(Pontoppidan, 1763)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1198,6 +1188,11 @@
           <t>2026-05-27</t>
         </is>
       </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Från närbelägen sjö eller våtmark</t>
+        </is>
+      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
@@ -1226,27 +1221,27 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>134033032</v>
+        <v>134032932</v>
       </c>
       <c r="B7" t="n">
-        <v>57972</v>
+        <v>57280</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>100065</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Trana</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Grus grus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1335,27 +1330,27 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>134032013</v>
+        <v>134033641</v>
       </c>
       <c r="B8" t="n">
-        <v>58234</v>
+        <v>57386</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>102981</v>
+        <v>102954</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Hussvala</t>
+          <t>Enkelbeckasin</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Delichon urbicum</t>
+          <t>Gallinago gallinago</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1416,6 +1411,11 @@
           <t>2026-05-27</t>
         </is>
       </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Spelflykt</t>
+        </is>
+      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
@@ -1444,32 +1444,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>134032994</v>
+        <v>134033720</v>
       </c>
       <c r="B9" t="n">
-        <v>58457</v>
+        <v>57796</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100058</v>
+        <v>102976</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mindre flugsnappare</t>
+          <t>Tornseglare</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Ficedula parva</t>
+          <t>Apus apus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Bechstein, 1794)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1553,27 +1553,27 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>134032932</v>
+        <v>134032013</v>
       </c>
       <c r="B10" t="n">
-        <v>57280</v>
+        <v>58234</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100065</v>
+        <v>102981</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Trana</t>
+          <t>Hussvala</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Grus grus</t>
+          <t>Delichon urbicum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1662,32 +1662,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>134033641</v>
+        <v>134045219</v>
       </c>
       <c r="B11" t="n">
-        <v>57386</v>
+        <v>58260</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>102954</v>
+        <v>103012</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Enkelbeckasin</t>
+          <t>Grönsångare</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Gallinago gallinago</t>
+          <t>Phylloscopus sibilatrix</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Bechstein, 1793)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1743,11 +1743,6 @@
           <t>2026-05-27</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Spelflykt</t>
-        </is>
-      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
@@ -1776,10 +1771,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>134045177</v>
+        <v>134045236</v>
       </c>
       <c r="B12" t="n">
-        <v>58658</v>
+        <v>58349</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1787,16 +1782,16 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103044</v>
+        <v>103015</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1885,32 +1880,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>134033720</v>
+        <v>134045231</v>
       </c>
       <c r="B13" t="n">
-        <v>57796</v>
+        <v>58461</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>102976</v>
+        <v>103018</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tornseglare</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Apus apus</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pallas, 1764)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1994,32 +1989,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>134031752</v>
+        <v>134045246</v>
       </c>
       <c r="B14" t="n">
-        <v>57624</v>
+        <v>58131</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100063</v>
+        <v>103023</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Smålom</t>
+          <t>Tofsmes</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Gavia stellata</t>
+          <t>Lophophanes cristatus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Pontoppidan, 1763)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2075,11 +2070,6 @@
           <t>2026-05-27</t>
         </is>
       </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Från närbelägen sjö eller våtmark</t>
-        </is>
-      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
@@ -2101,6 +2091,115 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Örebro län LB</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>134045177</v>
+      </c>
+      <c r="B15" t="n">
+        <v>58658</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>103044</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Grönsiska</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Spinus spinus</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Stuttjärnsfall stora omr S, Vstm</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>498798</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6630831</v>
+      </c>
+      <c r="S15" t="n">
+        <v>100</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Ljusnarsberg</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Ljusnarsberg</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Maria Berdén Evertsson</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Maria Berdén Evertsson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr">
         <is>
           <t>Naturskyddsföreningen Örebro län LB</t>
         </is>

--- a/artfynd/A 19645-2026 artfynd.xlsx
+++ b/artfynd/A 19645-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY15"/>
+  <dimension ref="A1:AZ15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121853586</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -886,6 +896,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121853587</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -995,6 +1010,11 @@
           <t>Naturskyddsföreningen Örebro län LB</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134033032</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1104,6 +1124,11 @@
           <t>Naturskyddsföreningen Örebro län LB</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134032994</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1218,6 +1243,11 @@
           <t>Naturskyddsföreningen Örebro län LB</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134031752</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1327,6 +1357,11 @@
           <t>Naturskyddsföreningen Örebro län LB</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134032932</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1441,6 +1476,11 @@
           <t>Naturskyddsföreningen Örebro län LB</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134033641</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1550,6 +1590,11 @@
           <t>Naturskyddsföreningen Örebro län LB</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134033720</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1659,6 +1704,11 @@
           <t>Naturskyddsföreningen Örebro län LB</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134032013</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1768,6 +1818,11 @@
           <t>Naturskyddsföreningen Örebro län LB</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134045219</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1877,6 +1932,11 @@
           <t>Naturskyddsföreningen Örebro län LB</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134045236</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1986,6 +2046,11 @@
           <t>Naturskyddsföreningen Örebro län LB</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134045231</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2095,6 +2160,11 @@
           <t>Naturskyddsföreningen Örebro län LB</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134045246</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2204,8 +2274,29 @@
           <t>Naturskyddsföreningen Örebro län LB</t>
         </is>
       </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134045177</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>